--- a/medicaid-tracker/Medicaid Enrollment Tracker.xlsx
+++ b/medicaid-tracker/Medicaid Enrollment Tracker.xlsx
@@ -6486,7 +6486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 17:25</t>
+          <t>2026-10-16 17:45</t>
         </is>
       </c>
     </row>
